--- a/reference/thong_ke_dau/Book1.xlsx
+++ b/reference/thong_ke_dau/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hungnguyen09/Side_Project/PhuPhatCorp/web_v2/reference/thong_ke_dau/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C6ADA3-A494-984A-84E2-6326C7CC8535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30CFEAF-629B-C24C-982A-18D1F2677B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="920" windowWidth="21880" windowHeight="16040" xr2:uid="{C3A41CFF-ECFE-4734-9E4B-D258F64C4330}"/>
   </bookViews>
